--- a/config/pricing.xlsx
+++ b/config/pricing.xlsx
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14" customWidth="1" style="10" min="1" max="1"/>
@@ -1947,640 +1947,6 @@
       <c r="H34" s="8" t="inlineStr">
         <is>
           <t>PREMIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>rwa_flat_ledger</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>rwa_receipt_tracking</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>rwa_member_directory</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>rwa_notice_board</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H38" s="16" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>rwa_complaint_tracking</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>rwa_broadcast_messaging</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H40" s="16" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>rwa_polls</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>rwa_visitor_pass</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>rwa_basic_reports</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H43" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>rwa_auto_billing</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>rwa_late_fees</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>rwa_facilities_booking</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>rwa_asset_register</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>rwa_advanced_reports</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H48" s="16" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>rwa_whatsapp_invoices</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>PRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>rwa_document_storage</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>PRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>rwa_vendor_management</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>PRO</t>
         </is>
       </c>
     </row>

--- a/config/pricing.xlsx
+++ b/config/pricing.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -924,46 +924,78 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Productivity</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>multi_user_2</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
+          <t>sticky_voucher_date</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Productivity</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>multi_user_5</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
+          <t>multi_party_voucher</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -973,71 +1005,51 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>multi_user_unlimited</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>multi_user_2</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>trial_balance</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>multi_user_5</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>profit_loss</t>
+          <t>multi_user_unlimited</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1046,26 +1058,14 @@
         </is>
       </c>
       <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>trial_balance</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>cash_book</t>
+          <t>profit_loss</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>bank_book</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ledger_account</t>
+          <t>cash_book</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>receipts_payments</t>
+          <t>bank_book</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1260,12 +1260,12 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>export_excel</t>
+          <t>ledger_account</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1298,12 +1298,12 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>export_pdf</t>
+          <t>receipts_payments</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>export_excel</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>email_report</t>
+          <t>export_pdf</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1412,12 +1412,12 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>bank_reconciliation</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1450,12 +1450,12 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ledger_reconciliation</t>
+          <t>email_report</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1488,12 +1488,12 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Reconciliation</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>book_migration</t>
+          <t>bank_reconciliation</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1526,12 +1526,12 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Reconciliation</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>gst</t>
+          <t>bank_reco_split</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1540,7 +1540,11 @@
         </is>
       </c>
       <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1553,19 +1557,19 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>STANDARD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Reconciliation</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>tds</t>
+          <t>ledger_reconciliation</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1574,7 +1578,11 @@
         </is>
       </c>
       <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1587,19 +1595,19 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>STANDARD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ai_document_reader</t>
+          <t>book_migration</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1608,7 +1616,11 @@
         </is>
       </c>
       <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1621,19 +1633,19 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>STANDARD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>verbal_entry</t>
+          <t>gst</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1662,12 +1674,12 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>auto_billing</t>
+          <t>tds</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1696,12 +1708,12 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>ai_document_reader</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1711,7 +1723,11 @@
       </c>
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1719,19 +1735,19 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>PRO</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>audit_export</t>
+          <t>verbal_entry</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1741,7 +1757,11 @@
       </c>
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1749,19 +1769,19 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>PRO</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>api_access</t>
+          <t>auto_billing</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1771,7 +1791,11 @@
       </c>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1779,7 +1803,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>PRO</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1815,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>verticals</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1808,6 +1832,96 @@
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>audit_export</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>api_access</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>verticals</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
@@ -1819,10 +1933,10 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DEMO,FREE,STANDARD,PRO,PREMIUM"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/pricing.xlsx
+++ b/config/pricing.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1602,12 +1602,12 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Reconciliation</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>book_migration</t>
+          <t>ledger_reco_split</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1640,12 +1640,12 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>gst</t>
+          <t>book_migration</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1654,7 +1654,11 @@
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1667,7 +1671,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>STANDARD</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1683,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>tds</t>
+          <t>gst</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1708,12 +1712,12 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ai_document_reader</t>
+          <t>tds</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1747,7 +1751,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>verbal_entry</t>
+          <t>ai_document_reader</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1781,7 +1785,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>auto_billing</t>
+          <t>verbal_entry</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1810,12 +1814,12 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>auto_billing</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1825,7 +1829,11 @@
       </c>
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1833,7 +1841,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>PRO</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1853,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>audit_export</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -1875,7 +1883,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>api_access</t>
+          <t>audit_export</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1905,7 +1913,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>verticals</t>
+          <t>api_access</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -1922,6 +1930,36 @@
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>verticals</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
@@ -1933,10 +1971,10 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:G38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DEMO,FREE,STANDARD,PRO,PREMIUM"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/pricing.xlsx
+++ b/config/pricing.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1336,12 +1336,12 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>export_excel</t>
+          <t>receivables_aging</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>export_pdf</t>
+          <t>export_excel</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>export_pdf</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>email_report</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1488,12 +1488,12 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>bank_reconciliation</t>
+          <t>email_report</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>bank_reco_split</t>
+          <t>bank_reconciliation</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ledger_reconciliation</t>
+          <t>bank_reco_split</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ledger_reco_split</t>
+          <t>ledger_reconciliation</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1640,12 +1640,12 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Reconciliation</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>book_migration</t>
+          <t>ledger_reco_split</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1678,12 +1678,12 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>gst</t>
+          <t>book_migration</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1692,7 +1692,11 @@
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1705,7 +1709,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>STANDARD</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1721,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>tds</t>
+          <t>gst</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1746,12 +1750,12 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ai_document_reader</t>
+          <t>tds</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1785,7 +1789,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>verbal_entry</t>
+          <t>ai_document_reader</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1819,7 +1823,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>auto_billing</t>
+          <t>verbal_entry</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1848,12 +1852,12 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>auto_billing</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -1863,7 +1867,11 @@
       </c>
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1871,7 +1879,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>PRO</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1891,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>audit_export</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1913,7 +1921,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>api_access</t>
+          <t>audit_export</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -1943,7 +1951,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>verticals</t>
+          <t>api_access</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1960,6 +1968,36 @@
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>verticals</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>PREMIUM</t>
         </is>
@@ -1971,10 +2009,10 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:G38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:G39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"DEMO,FREE,STANDARD,PRO,PREMIUM"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/pricing.xlsx
+++ b/config/pricing.xlsx
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14" customWidth="1" style="10" min="1" max="1"/>
@@ -2122,6 +2122,107 @@
         </is>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>bill_wise_refs</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>payables_aging</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>cash_flow_planning</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>PRO</t>
         </is>
